--- a/data/gravel/Wilier Jaroon 2025.xlsx
+++ b/data/gravel/Wilier Jaroon 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210E4080-8139-014A-9DD0-94AB9AD76BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BDDC6F-1313-0245-A4E8-05A46A820A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="640" windowWidth="24520" windowHeight="16120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17260" yWindow="-23700" windowWidth="24520" windowHeight="16120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>https://bikeinsights.com/bikes/5e6cbcf752899400175de590-wilier-triestina-jaroon</t>
   </si>
 </sst>
 </file>
@@ -1178,7 +1181,27 @@
       <c r="A19" t="s">
         <v>37</v>
       </c>
-      <c r="I19" s="1"/>
+      <c r="C19">
+        <v>70</v>
+      </c>
+      <c r="D19">
+        <v>70</v>
+      </c>
+      <c r="E19">
+        <v>70</v>
+      </c>
+      <c r="F19">
+        <v>70</v>
+      </c>
+      <c r="G19">
+        <v>70</v>
+      </c>
+      <c r="H19">
+        <v>70</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">

--- a/data/gravel/Wilier Jaroon 2025.xlsx
+++ b/data/gravel/Wilier Jaroon 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BDDC6F-1313-0245-A4E8-05A46A820A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFE9B6A-6E16-C647-80C5-4026E096907A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17260" yWindow="-23700" windowWidth="24520" windowHeight="16120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -59,9 +59,6 @@
     <t>data_range</t>
   </si>
   <si>
-    <t>a8:h33</t>
-  </si>
-  <si>
     <t>frame_size</t>
   </si>
   <si>
@@ -83,9 +80,6 @@
     <t>XL</t>
   </si>
   <si>
-    <t>XXL</t>
-  </si>
-  <si>
     <t>seat_tube_cc</t>
   </si>
   <si>
@@ -348,6 +342,9 @@
   </si>
   <si>
     <t>https://bikeinsights.com/bikes/5e6cbcf752899400175de590-wilier-triestina-jaroon</t>
+  </si>
+  <si>
+    <t>a8:g33</t>
   </si>
 </sst>
 </file>
@@ -687,13 +684,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -701,15 +698,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -717,7 +714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -725,59 +722,56 @@
         <v>45950</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>12</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>13</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>14</v>
       </c>
-      <c r="G8" t="s">
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="H8" t="s">
+      <c r="B9" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
       </c>
       <c r="C9">
         <f>J9*10</f>
@@ -799,10 +793,6 @@
         <f t="shared" si="0"/>
         <v>510</v>
       </c>
-      <c r="H9">
-        <f t="shared" si="0"/>
-        <v>5420</v>
-      </c>
       <c r="J9">
         <v>39</v>
       </c>
@@ -818,16 +808,13 @@
       <c r="N9">
         <v>51</v>
       </c>
-      <c r="O9">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10">
         <f t="shared" ref="C10:C14" si="1">J10*10</f>
@@ -849,10 +836,6 @@
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="H10">
-        <f t="shared" si="0"/>
-        <v>5970</v>
-      </c>
       <c r="J10">
         <v>54</v>
       </c>
@@ -868,16 +851,13 @@
       <c r="N10">
         <v>60</v>
       </c>
-      <c r="O10">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
@@ -899,10 +879,6 @@
         <f t="shared" si="0"/>
         <v>560</v>
       </c>
-      <c r="H11">
-        <f t="shared" si="0"/>
-        <v>5600</v>
-      </c>
       <c r="J11">
         <v>44</v>
       </c>
@@ -918,16 +894,13 @@
       <c r="N11">
         <v>56</v>
       </c>
-      <c r="O11">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C12">
         <f>J12</f>
@@ -949,10 +922,6 @@
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="H12">
-        <f t="shared" si="2"/>
-        <v>73</v>
-      </c>
       <c r="J12">
         <v>74</v>
       </c>
@@ -968,16 +937,13 @@
       <c r="N12">
         <v>74</v>
       </c>
-      <c r="O12">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
@@ -999,10 +965,6 @@
         <f t="shared" ref="G13:G14" si="6">N13*10</f>
         <v>440</v>
       </c>
-      <c r="H13">
-        <f t="shared" ref="H13:H14" si="7">O13*10</f>
-        <v>4230</v>
-      </c>
       <c r="J13">
         <v>44</v>
       </c>
@@ -1018,16 +980,13 @@
       <c r="N13">
         <v>44</v>
       </c>
-      <c r="O13">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
@@ -1049,10 +1008,6 @@
         <f t="shared" si="6"/>
         <v>200</v>
       </c>
-      <c r="H14">
-        <f t="shared" si="7"/>
-        <v>1850</v>
-      </c>
       <c r="J14">
         <v>10</v>
       </c>
@@ -1068,16 +1023,13 @@
       <c r="N14">
         <v>20</v>
       </c>
-      <c r="O14">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C15">
         <v>70</v>
@@ -1094,16 +1046,13 @@
       <c r="G15">
         <v>70</v>
       </c>
-      <c r="H15">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C16">
         <v>384</v>
@@ -1120,16 +1069,13 @@
       <c r="G16">
         <v>417</v>
       </c>
-      <c r="H16">
-        <v>408</v>
-      </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>548</v>
@@ -1146,16 +1092,13 @@
       <c r="G17">
         <v>626</v>
       </c>
-      <c r="H17">
-        <v>617</v>
-      </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C18">
         <v>1037</v>
@@ -1172,14 +1115,11 @@
       <c r="G18">
         <v>1104</v>
       </c>
-      <c r="H18">
-        <v>1052</v>
-      </c>
       <c r="I18" s="1"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C19">
         <v>70</v>
@@ -1196,64 +1136,61 @@
       <c r="G19">
         <v>70</v>
       </c>
-      <c r="H19">
-        <v>70</v>
-      </c>
       <c r="I19" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C29">
         <v>700</v>
@@ -1270,16 +1207,13 @@
       <c r="G29">
         <v>700</v>
       </c>
-      <c r="H29">
-        <v>700</v>
-      </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C30">
         <v>40</v>
@@ -1296,16 +1230,13 @@
       <c r="G30">
         <v>40</v>
       </c>
-      <c r="H30">
-        <v>40</v>
-      </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C31">
         <v>45</v>
@@ -1322,79 +1253,76 @@
       <c r="G31">
         <v>45</v>
       </c>
-      <c r="H31">
-        <v>45</v>
-      </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B36" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B38" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B42">
         <v>45</v>
@@ -1402,32 +1330,32 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B48">
         <v>142</v>
@@ -1435,7 +1363,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B49">
         <v>100</v>
@@ -1443,18 +1371,18 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B50" s="1"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B52">
         <v>27.2</v>
@@ -1462,112 +1390,112 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B71">
         <v>1900</v>
@@ -1575,23 +1503,23 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B74" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Wilier Jaroon 2025.xlsx
+++ b/data/gravel/Wilier Jaroon 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFE9B6A-6E16-C647-80C5-4026E096907A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1332F7A6-897B-EF44-89CA-A24DF1D77A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17260" yWindow="-23700" windowWidth="24520" windowHeight="16120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -345,6 +345,24 @@
   </si>
   <si>
     <t>a8:g33</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -684,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N74"/>
+  <dimension ref="A1:N80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -778,7 +796,7 @@
         <v>390</v>
       </c>
       <c r="D9">
-        <f t="shared" ref="D9:H11" si="0">K9*10</f>
+        <f t="shared" ref="D9:G11" si="0">K9*10</f>
         <v>420</v>
       </c>
       <c r="E9">
@@ -907,7 +925,7 @@
         <v>74</v>
       </c>
       <c r="D12">
-        <f t="shared" ref="D12:H12" si="2">K12</f>
+        <f t="shared" ref="D12:G12" si="2">K12</f>
         <v>74</v>
       </c>
       <c r="E12">
@@ -1371,154 +1389,184 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>64</v>
-      </c>
-      <c r="B50" s="1"/>
+        <v>104</v>
+      </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>66</v>
-      </c>
-      <c r="B52">
-        <v>27.2</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>67</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>70</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="B56" s="1"/>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>72</v>
+        <v>66</v>
+      </c>
+      <c r="B58">
+        <v>27.2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>79</v>
+        <v>73</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>81</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>82</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>83</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>85</v>
-      </c>
-      <c r="B71">
-        <v>1900</v>
+        <v>79</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>94</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>95</v>
       </c>
     </row>
